--- a/testing/glm-mv-reference/spss-output/mv2_dua_populasi.xlsx
+++ b/testing/glm-mv-reference/spss-output/mv2_dua_populasi.xlsx
@@ -1014,87 +1014,87 @@
   </cellXfs>
   <cellStyles count="82">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="style1790153226171" xfId="1"/>
-    <cellStyle name="style1790153226237" xfId="2"/>
-    <cellStyle name="style1790153226295" xfId="3"/>
-    <cellStyle name="style1790153226333" xfId="4"/>
-    <cellStyle name="style1790153226362" xfId="5"/>
-    <cellStyle name="style1790153226388" xfId="6"/>
-    <cellStyle name="style1790153226408" xfId="7"/>
-    <cellStyle name="style1790153226437" xfId="8"/>
-    <cellStyle name="style1790153226463" xfId="9"/>
-    <cellStyle name="style1790153226492" xfId="10"/>
-    <cellStyle name="style1790153226519" xfId="11"/>
-    <cellStyle name="style1790153226546" xfId="12"/>
-    <cellStyle name="style1790153226572" xfId="13"/>
-    <cellStyle name="style1790153226602" xfId="14"/>
-    <cellStyle name="style1790153226630" xfId="15"/>
-    <cellStyle name="style1790153226647" xfId="16"/>
-    <cellStyle name="style1790153226668" xfId="17"/>
-    <cellStyle name="style1790153226696" xfId="18"/>
-    <cellStyle name="style1790153226724" xfId="19"/>
-    <cellStyle name="style1790153226753" xfId="20"/>
-    <cellStyle name="style1790153226782" xfId="21"/>
-    <cellStyle name="style1790153226811" xfId="22"/>
-    <cellStyle name="style1790153226828" xfId="23"/>
-    <cellStyle name="style1790153226861" xfId="24"/>
-    <cellStyle name="style1790153226884" xfId="25"/>
-    <cellStyle name="style1790153226909" xfId="26"/>
-    <cellStyle name="style1790153226933" xfId="27"/>
-    <cellStyle name="style1790153226958" xfId="28"/>
-    <cellStyle name="style1790153226982" xfId="29"/>
-    <cellStyle name="style1790153227017" xfId="30"/>
-    <cellStyle name="style1790153227044" xfId="31"/>
-    <cellStyle name="style1790153227066" xfId="32"/>
-    <cellStyle name="style1790153227093" xfId="33"/>
-    <cellStyle name="style1790153227111" xfId="34"/>
-    <cellStyle name="style1790153227135" xfId="35"/>
-    <cellStyle name="style1790153227156" xfId="36"/>
-    <cellStyle name="style1790153227181" xfId="37"/>
-    <cellStyle name="style1790153227205" xfId="38"/>
-    <cellStyle name="style1790153227230" xfId="39"/>
-    <cellStyle name="style1790153227251" xfId="40"/>
-    <cellStyle name="style1790153227276" xfId="41"/>
-    <cellStyle name="style1790153227293" xfId="42"/>
-    <cellStyle name="style1790153227317" xfId="43"/>
-    <cellStyle name="style1790153227332" xfId="44"/>
-    <cellStyle name="style1790153227349" xfId="45"/>
-    <cellStyle name="style1790153227369" xfId="46"/>
-    <cellStyle name="style1790153227387" xfId="47"/>
-    <cellStyle name="style1790153227406" xfId="48"/>
-    <cellStyle name="style1790153227420" xfId="49"/>
-    <cellStyle name="style1790153227443" xfId="50"/>
-    <cellStyle name="style1790153227460" xfId="51"/>
-    <cellStyle name="style1790153227479" xfId="52"/>
-    <cellStyle name="style1790153227498" xfId="53"/>
-    <cellStyle name="style1790153227521" xfId="54"/>
-    <cellStyle name="style1790153227543" xfId="55"/>
-    <cellStyle name="style1790153227559" xfId="56"/>
-    <cellStyle name="style1790153227574" xfId="57"/>
-    <cellStyle name="style1790153227586" xfId="58"/>
-    <cellStyle name="style1790153227604" xfId="59"/>
-    <cellStyle name="style1790153227622" xfId="60"/>
-    <cellStyle name="style1790153227637" xfId="61"/>
-    <cellStyle name="style1790153227654" xfId="62"/>
-    <cellStyle name="style1790153227671" xfId="63"/>
-    <cellStyle name="style1790153227688" xfId="64"/>
-    <cellStyle name="style1790153227707" xfId="65"/>
-    <cellStyle name="style1790153227723" xfId="66"/>
-    <cellStyle name="style1790153227742" xfId="67"/>
-    <cellStyle name="style1790153227767" xfId="68"/>
-    <cellStyle name="style1790153227786" xfId="69"/>
-    <cellStyle name="style1790153227801" xfId="70"/>
-    <cellStyle name="style1790153227823" xfId="71"/>
-    <cellStyle name="style1790153227845" xfId="72"/>
-    <cellStyle name="style1790153227867" xfId="73"/>
-    <cellStyle name="style1790153227882" xfId="74"/>
-    <cellStyle name="style1790153227903" xfId="75"/>
-    <cellStyle name="style1790153227919" xfId="76"/>
-    <cellStyle name="style1790153227940" xfId="77"/>
-    <cellStyle name="style1790153227955" xfId="78"/>
-    <cellStyle name="style1790153227973" xfId="79"/>
-    <cellStyle name="style1790153227992" xfId="80"/>
-    <cellStyle name="style1790153228008" xfId="81"/>
+    <cellStyle name="style1791026649001" xfId="1"/>
+    <cellStyle name="style1791026649047" xfId="2"/>
+    <cellStyle name="style1791026649074" xfId="3"/>
+    <cellStyle name="style1791026649107" xfId="4"/>
+    <cellStyle name="style1791026649138" xfId="5"/>
+    <cellStyle name="style1791026649169" xfId="6"/>
+    <cellStyle name="style1791026649191" xfId="7"/>
+    <cellStyle name="style1791026649226" xfId="8"/>
+    <cellStyle name="style1791026649251" xfId="9"/>
+    <cellStyle name="style1791026649282" xfId="10"/>
+    <cellStyle name="style1791026649313" xfId="11"/>
+    <cellStyle name="style1791026649341" xfId="12"/>
+    <cellStyle name="style1791026649369" xfId="13"/>
+    <cellStyle name="style1791026649403" xfId="14"/>
+    <cellStyle name="style1791026649435" xfId="15"/>
+    <cellStyle name="style1791026649456" xfId="16"/>
+    <cellStyle name="style1791026649478" xfId="17"/>
+    <cellStyle name="style1791026649505" xfId="18"/>
+    <cellStyle name="style1791026649535" xfId="19"/>
+    <cellStyle name="style1791026649566" xfId="20"/>
+    <cellStyle name="style1791026649592" xfId="21"/>
+    <cellStyle name="style1791026649615" xfId="22"/>
+    <cellStyle name="style1791026649636" xfId="23"/>
+    <cellStyle name="style1791026649655" xfId="24"/>
+    <cellStyle name="style1791026649685" xfId="25"/>
+    <cellStyle name="style1791026649713" xfId="26"/>
+    <cellStyle name="style1791026649742" xfId="27"/>
+    <cellStyle name="style1791026649772" xfId="28"/>
+    <cellStyle name="style1791026649799" xfId="29"/>
+    <cellStyle name="style1791026649828" xfId="30"/>
+    <cellStyle name="style1791026649850" xfId="31"/>
+    <cellStyle name="style1791026649877" xfId="32"/>
+    <cellStyle name="style1791026649903" xfId="33"/>
+    <cellStyle name="style1791026649923" xfId="34"/>
+    <cellStyle name="style1791026649948" xfId="35"/>
+    <cellStyle name="style1791026649974" xfId="36"/>
+    <cellStyle name="style1791026649996" xfId="37"/>
+    <cellStyle name="style1791026650024" xfId="38"/>
+    <cellStyle name="style1791026650050" xfId="39"/>
+    <cellStyle name="style1791026650074" xfId="40"/>
+    <cellStyle name="style1791026650101" xfId="41"/>
+    <cellStyle name="style1791026650122" xfId="42"/>
+    <cellStyle name="style1791026650144" xfId="43"/>
+    <cellStyle name="style1791026650169" xfId="44"/>
+    <cellStyle name="style1791026650187" xfId="45"/>
+    <cellStyle name="style1791026650207" xfId="46"/>
+    <cellStyle name="style1791026650225" xfId="47"/>
+    <cellStyle name="style1791026650244" xfId="48"/>
+    <cellStyle name="style1791026650262" xfId="49"/>
+    <cellStyle name="style1791026650286" xfId="50"/>
+    <cellStyle name="style1791026650308" xfId="51"/>
+    <cellStyle name="style1791026650329" xfId="52"/>
+    <cellStyle name="style1791026650354" xfId="53"/>
+    <cellStyle name="style1791026650379" xfId="54"/>
+    <cellStyle name="style1791026650407" xfId="55"/>
+    <cellStyle name="style1791026650428" xfId="56"/>
+    <cellStyle name="style1791026650447" xfId="57"/>
+    <cellStyle name="style1791026650463" xfId="58"/>
+    <cellStyle name="style1791026650475" xfId="59"/>
+    <cellStyle name="style1791026650500" xfId="60"/>
+    <cellStyle name="style1791026650517" xfId="61"/>
+    <cellStyle name="style1791026650538" xfId="62"/>
+    <cellStyle name="style1791026650554" xfId="63"/>
+    <cellStyle name="style1791026650573" xfId="64"/>
+    <cellStyle name="style1791026650590" xfId="65"/>
+    <cellStyle name="style1791026650605" xfId="66"/>
+    <cellStyle name="style1791026650621" xfId="67"/>
+    <cellStyle name="style1791026650657" xfId="68"/>
+    <cellStyle name="style1791026650674" xfId="69"/>
+    <cellStyle name="style1791026650690" xfId="70"/>
+    <cellStyle name="style1791026650709" xfId="71"/>
+    <cellStyle name="style1791026650735" xfId="72"/>
+    <cellStyle name="style1791026650761" xfId="73"/>
+    <cellStyle name="style1791026650779" xfId="74"/>
+    <cellStyle name="style1791026650796" xfId="75"/>
+    <cellStyle name="style1791026650816" xfId="76"/>
+    <cellStyle name="style1791026650833" xfId="77"/>
+    <cellStyle name="style1791026650852" xfId="78"/>
+    <cellStyle name="style1791026650867" xfId="79"/>
+    <cellStyle name="style1791026650887" xfId="80"/>
+    <cellStyle name="style1791026650903" xfId="81"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1499,7 +1499,7 @@
       <c r="B18" s="8"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>23-SEP-2026 15:47:05</t>
+          <t>03-OCT-2026 18:24:08</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>00:00:00.00</t>
+          <t>00:00:00.02</t>
         </is>
       </c>
     </row>

--- a/testing/glm-mv-reference/spss-output/mv2_dua_populasi.xlsx
+++ b/testing/glm-mv-reference/spss-output/mv2_dua_populasi.xlsx
@@ -1014,87 +1014,87 @@
   </cellXfs>
   <cellStyles count="82">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="style1791026649001" xfId="1"/>
-    <cellStyle name="style1791026649047" xfId="2"/>
-    <cellStyle name="style1791026649074" xfId="3"/>
-    <cellStyle name="style1791026649107" xfId="4"/>
-    <cellStyle name="style1791026649138" xfId="5"/>
-    <cellStyle name="style1791026649169" xfId="6"/>
-    <cellStyle name="style1791026649191" xfId="7"/>
-    <cellStyle name="style1791026649226" xfId="8"/>
-    <cellStyle name="style1791026649251" xfId="9"/>
-    <cellStyle name="style1791026649282" xfId="10"/>
-    <cellStyle name="style1791026649313" xfId="11"/>
-    <cellStyle name="style1791026649341" xfId="12"/>
-    <cellStyle name="style1791026649369" xfId="13"/>
-    <cellStyle name="style1791026649403" xfId="14"/>
-    <cellStyle name="style1791026649435" xfId="15"/>
-    <cellStyle name="style1791026649456" xfId="16"/>
-    <cellStyle name="style1791026649478" xfId="17"/>
-    <cellStyle name="style1791026649505" xfId="18"/>
-    <cellStyle name="style1791026649535" xfId="19"/>
-    <cellStyle name="style1791026649566" xfId="20"/>
-    <cellStyle name="style1791026649592" xfId="21"/>
-    <cellStyle name="style1791026649615" xfId="22"/>
-    <cellStyle name="style1791026649636" xfId="23"/>
-    <cellStyle name="style1791026649655" xfId="24"/>
-    <cellStyle name="style1791026649685" xfId="25"/>
-    <cellStyle name="style1791026649713" xfId="26"/>
-    <cellStyle name="style1791026649742" xfId="27"/>
-    <cellStyle name="style1791026649772" xfId="28"/>
-    <cellStyle name="style1791026649799" xfId="29"/>
-    <cellStyle name="style1791026649828" xfId="30"/>
-    <cellStyle name="style1791026649850" xfId="31"/>
-    <cellStyle name="style1791026649877" xfId="32"/>
-    <cellStyle name="style1791026649903" xfId="33"/>
-    <cellStyle name="style1791026649923" xfId="34"/>
-    <cellStyle name="style1791026649948" xfId="35"/>
-    <cellStyle name="style1791026649974" xfId="36"/>
-    <cellStyle name="style1791026649996" xfId="37"/>
-    <cellStyle name="style1791026650024" xfId="38"/>
-    <cellStyle name="style1791026650050" xfId="39"/>
-    <cellStyle name="style1791026650074" xfId="40"/>
-    <cellStyle name="style1791026650101" xfId="41"/>
-    <cellStyle name="style1791026650122" xfId="42"/>
-    <cellStyle name="style1791026650144" xfId="43"/>
-    <cellStyle name="style1791026650169" xfId="44"/>
-    <cellStyle name="style1791026650187" xfId="45"/>
-    <cellStyle name="style1791026650207" xfId="46"/>
-    <cellStyle name="style1791026650225" xfId="47"/>
-    <cellStyle name="style1791026650244" xfId="48"/>
-    <cellStyle name="style1791026650262" xfId="49"/>
-    <cellStyle name="style1791026650286" xfId="50"/>
-    <cellStyle name="style1791026650308" xfId="51"/>
-    <cellStyle name="style1791026650329" xfId="52"/>
-    <cellStyle name="style1791026650354" xfId="53"/>
-    <cellStyle name="style1791026650379" xfId="54"/>
-    <cellStyle name="style1791026650407" xfId="55"/>
-    <cellStyle name="style1791026650428" xfId="56"/>
-    <cellStyle name="style1791026650447" xfId="57"/>
-    <cellStyle name="style1791026650463" xfId="58"/>
-    <cellStyle name="style1791026650475" xfId="59"/>
-    <cellStyle name="style1791026650500" xfId="60"/>
-    <cellStyle name="style1791026650517" xfId="61"/>
-    <cellStyle name="style1791026650538" xfId="62"/>
-    <cellStyle name="style1791026650554" xfId="63"/>
-    <cellStyle name="style1791026650573" xfId="64"/>
-    <cellStyle name="style1791026650590" xfId="65"/>
-    <cellStyle name="style1791026650605" xfId="66"/>
-    <cellStyle name="style1791026650621" xfId="67"/>
-    <cellStyle name="style1791026650657" xfId="68"/>
-    <cellStyle name="style1791026650674" xfId="69"/>
-    <cellStyle name="style1791026650690" xfId="70"/>
-    <cellStyle name="style1791026650709" xfId="71"/>
-    <cellStyle name="style1791026650735" xfId="72"/>
-    <cellStyle name="style1791026650761" xfId="73"/>
-    <cellStyle name="style1791026650779" xfId="74"/>
-    <cellStyle name="style1791026650796" xfId="75"/>
-    <cellStyle name="style1791026650816" xfId="76"/>
-    <cellStyle name="style1791026650833" xfId="77"/>
-    <cellStyle name="style1791026650852" xfId="78"/>
-    <cellStyle name="style1791026650867" xfId="79"/>
-    <cellStyle name="style1791026650887" xfId="80"/>
-    <cellStyle name="style1791026650903" xfId="81"/>
+    <cellStyle name="style1790153226171" xfId="1"/>
+    <cellStyle name="style1790153226237" xfId="2"/>
+    <cellStyle name="style1790153226295" xfId="3"/>
+    <cellStyle name="style1790153226333" xfId="4"/>
+    <cellStyle name="style1790153226362" xfId="5"/>
+    <cellStyle name="style1790153226388" xfId="6"/>
+    <cellStyle name="style1790153226408" xfId="7"/>
+    <cellStyle name="style1790153226437" xfId="8"/>
+    <cellStyle name="style1790153226463" xfId="9"/>
+    <cellStyle name="style1790153226492" xfId="10"/>
+    <cellStyle name="style1790153226519" xfId="11"/>
+    <cellStyle name="style1790153226546" xfId="12"/>
+    <cellStyle name="style1790153226572" xfId="13"/>
+    <cellStyle name="style1790153226602" xfId="14"/>
+    <cellStyle name="style1790153226630" xfId="15"/>
+    <cellStyle name="style1790153226647" xfId="16"/>
+    <cellStyle name="style1790153226668" xfId="17"/>
+    <cellStyle name="style1790153226696" xfId="18"/>
+    <cellStyle name="style1790153226724" xfId="19"/>
+    <cellStyle name="style1790153226753" xfId="20"/>
+    <cellStyle name="style1790153226782" xfId="21"/>
+    <cellStyle name="style1790153226811" xfId="22"/>
+    <cellStyle name="style1790153226828" xfId="23"/>
+    <cellStyle name="style1790153226861" xfId="24"/>
+    <cellStyle name="style1790153226884" xfId="25"/>
+    <cellStyle name="style1790153226909" xfId="26"/>
+    <cellStyle name="style1790153226933" xfId="27"/>
+    <cellStyle name="style1790153226958" xfId="28"/>
+    <cellStyle name="style1790153226982" xfId="29"/>
+    <cellStyle name="style1790153227017" xfId="30"/>
+    <cellStyle name="style1790153227044" xfId="31"/>
+    <cellStyle name="style1790153227066" xfId="32"/>
+    <cellStyle name="style1790153227093" xfId="33"/>
+    <cellStyle name="style1790153227111" xfId="34"/>
+    <cellStyle name="style1790153227135" xfId="35"/>
+    <cellStyle name="style1790153227156" xfId="36"/>
+    <cellStyle name="style1790153227181" xfId="37"/>
+    <cellStyle name="style1790153227205" xfId="38"/>
+    <cellStyle name="style1790153227230" xfId="39"/>
+    <cellStyle name="style1790153227251" xfId="40"/>
+    <cellStyle name="style1790153227276" xfId="41"/>
+    <cellStyle name="style1790153227293" xfId="42"/>
+    <cellStyle name="style1790153227317" xfId="43"/>
+    <cellStyle name="style1790153227332" xfId="44"/>
+    <cellStyle name="style1790153227349" xfId="45"/>
+    <cellStyle name="style1790153227369" xfId="46"/>
+    <cellStyle name="style1790153227387" xfId="47"/>
+    <cellStyle name="style1790153227406" xfId="48"/>
+    <cellStyle name="style1790153227420" xfId="49"/>
+    <cellStyle name="style1790153227443" xfId="50"/>
+    <cellStyle name="style1790153227460" xfId="51"/>
+    <cellStyle name="style1790153227479" xfId="52"/>
+    <cellStyle name="style1790153227498" xfId="53"/>
+    <cellStyle name="style1790153227521" xfId="54"/>
+    <cellStyle name="style1790153227543" xfId="55"/>
+    <cellStyle name="style1790153227559" xfId="56"/>
+    <cellStyle name="style1790153227574" xfId="57"/>
+    <cellStyle name="style1790153227586" xfId="58"/>
+    <cellStyle name="style1790153227604" xfId="59"/>
+    <cellStyle name="style1790153227622" xfId="60"/>
+    <cellStyle name="style1790153227637" xfId="61"/>
+    <cellStyle name="style1790153227654" xfId="62"/>
+    <cellStyle name="style1790153227671" xfId="63"/>
+    <cellStyle name="style1790153227688" xfId="64"/>
+    <cellStyle name="style1790153227707" xfId="65"/>
+    <cellStyle name="style1790153227723" xfId="66"/>
+    <cellStyle name="style1790153227742" xfId="67"/>
+    <cellStyle name="style1790153227767" xfId="68"/>
+    <cellStyle name="style1790153227786" xfId="69"/>
+    <cellStyle name="style1790153227801" xfId="70"/>
+    <cellStyle name="style1790153227823" xfId="71"/>
+    <cellStyle name="style1790153227845" xfId="72"/>
+    <cellStyle name="style1790153227867" xfId="73"/>
+    <cellStyle name="style1790153227882" xfId="74"/>
+    <cellStyle name="style1790153227903" xfId="75"/>
+    <cellStyle name="style1790153227919" xfId="76"/>
+    <cellStyle name="style1790153227940" xfId="77"/>
+    <cellStyle name="style1790153227955" xfId="78"/>
+    <cellStyle name="style1790153227973" xfId="79"/>
+    <cellStyle name="style1790153227992" xfId="80"/>
+    <cellStyle name="style1790153228008" xfId="81"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1499,7 +1499,7 @@
       <c r="B18" s="8"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>03-OCT-2026 18:24:08</t>
+          <t>23-SEP-2026 15:47:05</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>00:00:00.02</t>
+          <t>00:00:00.00</t>
         </is>
       </c>
     </row>
